--- a/Claude outputs/brook street quarantine 07.26 data FIXED.xlsx
+++ b/Claude outputs/brook street quarantine 07.26 data FIXED.xlsx
@@ -1641,7 +1641,11 @@
           <t>Pink</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Womens</t>
